--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81A286C-C3CB-C24A-ADDB-00A3BA3BB3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FB3E0F-986A-0442-A218-0DEC812B951D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10560" yWindow="500" windowWidth="15880" windowHeight="16080" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
+    <workbookView xWindow="10560" yWindow="500" windowWidth="15880" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>exp1_plausibility</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>list_8</t>
+  </si>
+  <si>
+    <t>11 (1 missed upload)</t>
   </si>
 </sst>
 </file>
@@ -105,12 +108,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -125,8 +140,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,7 +461,7 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="18.1640625" customWidth="1"/>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
@@ -483,10 +500,16 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
+      </c>
+      <c r="B3" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FB3E0F-986A-0442-A218-0DEC812B951D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64490E0-97D0-3448-8378-DA8BDDEE6AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10560" yWindow="500" windowWidth="15880" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
+    <workbookView xWindow="5200" yWindow="500" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -508,7 +508,7 @@
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>10</v>
       </c>
     </row>
@@ -516,10 +516,16 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
+      <c r="B4" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64490E0-97D0-3448-8378-DA8BDDEE6AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139B11E1-A0F1-C742-A766-71A7A77134E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="500" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -524,13 +524,16 @@
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
+      </c>
+      <c r="B6" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139B11E1-A0F1-C742-A766-71A7A77134E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA03CB9F-A541-4D40-AFAB-9D891C3535FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="500" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -532,7 +532,7 @@
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>10</v>
       </c>
     </row>
@@ -540,10 +540,16 @@
       <c r="A7" t="s">
         <v>13</v>
       </c>
+      <c r="B7" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
+      </c>
+      <c r="B8" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA03CB9F-A541-4D40-AFAB-9D891C3535FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F323C77C-2DEC-934E-8746-3BFF8BBEEA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="500" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -548,13 +548,16 @@
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
+      </c>
+      <c r="B9" s="2">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F323C77C-2DEC-934E-8746-3BFF8BBEEA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF843A9-83FF-F148-984D-FA727A52D4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="500" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
+    <workbookView minimized="1" xWindow="5200" yWindow="500" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -117,13 +117,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -140,10 +134,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,7 +549,7 @@
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>10</v>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF843A9-83FF-F148-984D-FA727A52D4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7822E7-4208-3649-9ED3-AA8F99C33BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5200" yWindow="500" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
+    <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
   <si>
     <t>exp1_plausibility</t>
   </si>
@@ -47,21 +47,6 @@
     <t>exp3_physical_states</t>
   </si>
   <si>
-    <t>exp4_places</t>
-  </si>
-  <si>
-    <t>exp5_valence</t>
-  </si>
-  <si>
-    <t>exp6_arousal</t>
-  </si>
-  <si>
-    <t>exp7_imageability</t>
-  </si>
-  <si>
-    <t>exp8_perceived_general_frequency</t>
-  </si>
-  <si>
     <t>list_1</t>
   </si>
   <si>
@@ -87,6 +72,24 @@
   </si>
   <si>
     <t>11 (1 missed upload)</t>
+  </si>
+  <si>
+    <t>code changed</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>prolific study made</t>
+  </si>
+  <si>
+    <t>tested</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>sanity check</t>
   </si>
 </sst>
 </file>
@@ -108,7 +111,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -121,8 +124,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -130,13 +145,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -155,9 +216,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -195,7 +256,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -301,7 +362,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -443,7 +504,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -451,9 +512,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485D37D3-95E4-E746-9471-DD8244642BCE}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.1640625" customWidth="1"/>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -461,96 +523,270 @@
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B6" s="5">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B7" s="5">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B8" s="5">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B9" s="5">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B10" s="5">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B11" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B12" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1">
-        <v>10</v>
+      <c r="C13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7822E7-4208-3649-9ED3-AA8F99C33BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D63355D-70E5-C040-BC05-6083E222F30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="20">
   <si>
     <t>exp1_plausibility</t>
   </si>
@@ -90,6 +91,12 @@
   </si>
   <si>
     <t>sanity check</t>
+  </si>
+  <si>
+    <t>12 (1 missed , 1 rejected)</t>
+  </si>
+  <si>
+    <t>yes (old, free, fixed)</t>
   </si>
 </sst>
 </file>
@@ -111,7 +118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,6 +140,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -188,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -198,6 +211,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,8 +603,8 @@
       <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>16</v>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>16</v>
@@ -618,8 +632,8 @@
       <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>16</v>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>16</v>
@@ -647,7 +661,9 @@
       <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -662,7 +678,9 @@
       <c r="B6" s="5">
         <v>10</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="9">
+        <v>10</v>
+      </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D63355D-70E5-C040-BC05-6083E222F30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81A441F-F0CD-354A-9B72-6EB4F52789A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
   <si>
     <t>exp1_plausibility</t>
   </si>
@@ -97,6 +97,21 @@
   </si>
   <si>
     <t>yes (old, free, fixed)</t>
+  </si>
+  <si>
+    <t>exp4_places</t>
+  </si>
+  <si>
+    <t>exp5_valence</t>
+  </si>
+  <si>
+    <t>exp6_arousal</t>
+  </si>
+  <si>
+    <t>exp7_imageability</t>
+  </si>
+  <si>
+    <t>exp8_perceived_general_frequency</t>
   </si>
 </sst>
 </file>
@@ -552,19 +567,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -678,7 +693,7 @@
       <c r="B6" s="5">
         <v>10</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="5">
         <v>10</v>
       </c>
       <c r="D6" s="2"/>
@@ -695,7 +710,9 @@
       <c r="B7" s="5">
         <v>10</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="5">
+        <v>10</v>
+      </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -710,7 +727,9 @@
       <c r="B8" s="5">
         <v>10</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="5">
+        <v>10</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -725,7 +744,9 @@
       <c r="B9" s="5">
         <v>10</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="9">
+        <v>10</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81A441F-F0CD-354A-9B72-6EB4F52789A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F273DB65-E0E8-C348-B5B4-FCA713DFA02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -744,7 +744,7 @@
       <c r="B9" s="5">
         <v>10</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="5">
         <v>10</v>
       </c>
       <c r="D9" s="2"/>
@@ -761,7 +761,9 @@
       <c r="B10" s="5">
         <v>10</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="9">
+        <v>10</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F273DB65-E0E8-C348-B5B4-FCA713DFA02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0B3D30-922E-F74F-AEA9-1638A6BCC4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
+    <workbookView minimized="1" xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -761,7 +761,7 @@
       <c r="B10" s="5">
         <v>10</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="5">
         <v>10</v>
       </c>
       <c r="D10" s="2"/>
@@ -778,7 +778,9 @@
       <c r="B11" s="5">
         <v>10</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="5">
+        <v>10</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -793,7 +795,9 @@
       <c r="B12" s="5">
         <v>10</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="9">
+        <v>10</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0B3D30-922E-F74F-AEA9-1638A6BCC4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9858ECB5-CB12-D64C-A460-679F213F38C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
+    <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -592,14 +591,14 @@
       <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>16</v>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>16</v>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>16</v>
@@ -621,8 +620,8 @@
       <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>16</v>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>16</v>
@@ -650,8 +649,8 @@
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>16</v>
@@ -679,7 +678,9 @@
       <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="5">
+        <v>10</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -696,7 +697,9 @@
       <c r="C6" s="5">
         <v>10</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="9">
+        <v>10</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -795,7 +798,7 @@
       <c r="B12" s="5">
         <v>10</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="5">
         <v>10</v>
       </c>
       <c r="D12" s="2"/>
@@ -812,8 +815,8 @@
       <c r="B13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>16</v>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>16</v>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9858ECB5-CB12-D64C-A460-679F213F38C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7169B7-E803-D841-AB08-AD28E441B7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -697,7 +697,7 @@
       <c r="C6" s="5">
         <v>10</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="5">
         <v>10</v>
       </c>
       <c r="E6" s="2"/>
@@ -716,7 +716,9 @@
       <c r="C7" s="5">
         <v>10</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="5">
+        <v>10</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -733,7 +735,9 @@
       <c r="C8" s="5">
         <v>10</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="9">
+        <v>10</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7169B7-E803-D841-AB08-AD28E441B7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F918B7F-00BD-DE47-A3F7-8849B4E6E448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -735,7 +735,7 @@
       <c r="C8" s="5">
         <v>10</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="5">
         <v>10</v>
       </c>
       <c r="E8" s="2"/>
@@ -754,7 +754,9 @@
       <c r="C9" s="5">
         <v>10</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="9">
+        <v>10</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F918B7F-00BD-DE47-A3F7-8849B4E6E448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918CE97A-14F3-6641-B518-953B6B241767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -131,8 +131,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,8 +166,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA9D08E"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -215,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -225,7 +238,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -773,7 +787,9 @@
       <c r="C10" s="5">
         <v>10</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="9">
+        <v>10</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -790,7 +806,9 @@
       <c r="C11" s="5">
         <v>10</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="10">
+        <v>10</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918CE97A-14F3-6641-B518-953B6B241767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1582543A-6BC9-084E-8F07-1AFD1674AE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -696,7 +696,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -806,7 +806,7 @@
       <c r="C11" s="5">
         <v>10</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>10</v>
       </c>
       <c r="E11" s="2"/>
@@ -825,7 +825,9 @@
       <c r="C12" s="5">
         <v>10</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="9">
+        <v>10</v>
+      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1582543A-6BC9-084E-8F07-1AFD1674AE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E7DE04-2CC1-A64D-8259-D4E16BA801CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -608,8 +608,8 @@
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>16</v>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>13</v>
@@ -637,11 +637,11 @@
       <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>16</v>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>16</v>
@@ -666,11 +666,11 @@
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>16</v>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>16</v>
@@ -695,8 +695,12 @@
       <c r="D5" s="5">
         <v>10</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="10"/>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -844,8 +848,8 @@
       <c r="C13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>16</v>
+      <c r="D13" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>16</v>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E7DE04-2CC1-A64D-8259-D4E16BA801CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71C5884-A02B-D346-B2A8-3E9CE56A38FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -695,11 +695,11 @@
       <c r="D5" s="5">
         <v>10</v>
       </c>
-      <c r="E5" s="10">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1</v>
+      <c r="E5" s="5">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5">
+        <v>10</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -718,8 +718,12 @@
       <c r="D6" s="5">
         <v>10</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="E6" s="5">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5">
+        <v>10</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -737,8 +741,12 @@
       <c r="D7" s="5">
         <v>10</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="E7" s="10">
+        <v>10</v>
+      </c>
+      <c r="F7" s="10">
+        <v>10</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71C5884-A02B-D346-B2A8-3E9CE56A38FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6F1286-D5D1-214B-A524-5D337F026FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -741,10 +741,10 @@
       <c r="D7" s="5">
         <v>10</v>
       </c>
-      <c r="E7" s="10">
-        <v>10</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="E7" s="5">
+        <v>10</v>
+      </c>
+      <c r="F7" s="5">
         <v>10</v>
       </c>
       <c r="G7" s="2"/>
@@ -764,8 +764,12 @@
       <c r="D8" s="5">
         <v>10</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="E8" s="10">
+        <v>10</v>
+      </c>
+      <c r="F8" s="10">
+        <v>10</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6F1286-D5D1-214B-A524-5D337F026FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424E627E-7441-8C49-A314-F3A49047E63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -764,10 +764,10 @@
       <c r="D8" s="5">
         <v>10</v>
       </c>
-      <c r="E8" s="10">
-        <v>10</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="E8" s="5">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5">
         <v>10</v>
       </c>
       <c r="G8" s="2"/>
@@ -787,8 +787,12 @@
       <c r="D9" s="9">
         <v>10</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="E9" s="5">
+        <v>10</v>
+      </c>
+      <c r="F9" s="5">
+        <v>10</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -806,8 +810,12 @@
       <c r="D10" s="9">
         <v>10</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="E10" s="10">
+        <v>10</v>
+      </c>
+      <c r="F10" s="10">
+        <v>10</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424E627E-7441-8C49-A314-F3A49047E63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEAAA36-8CBA-5C48-9BC5-BEC3F682CD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -810,10 +810,10 @@
       <c r="D10" s="9">
         <v>10</v>
       </c>
-      <c r="E10" s="10">
-        <v>10</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="E10" s="5">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5">
         <v>10</v>
       </c>
       <c r="G10" s="2"/>
@@ -833,8 +833,12 @@
       <c r="D11" s="9">
         <v>10</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="E11" s="10">
+        <v>10</v>
+      </c>
+      <c r="F11" s="10">
+        <v>10</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEAAA36-8CBA-5C48-9BC5-BEC3F682CD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D4FF9B-F972-4843-9933-E6660C598488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -139,7 +139,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -167,12 +167,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA9D08E"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -228,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -239,7 +233,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,10 +826,10 @@
       <c r="D11" s="9">
         <v>10</v>
       </c>
-      <c r="E11" s="10">
-        <v>10</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="E11" s="5">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
         <v>10</v>
       </c>
       <c r="G11" s="2"/>
@@ -856,8 +849,12 @@
       <c r="D12" s="9">
         <v>10</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="E12" s="5">
+        <v>10</v>
+      </c>
+      <c r="F12" s="5">
+        <v>10</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -875,11 +872,11 @@
       <c r="D13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>16</v>
+      <c r="E13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>16</v>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D4FF9B-F972-4843-9933-E6660C598488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FD0CBF-E679-9E48-8BEA-CF88649F5CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
+    <workbookView xWindow="5180" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -222,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -230,7 +230,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -607,14 +606,14 @@
       <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>16</v>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -636,14 +635,14 @@
       <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>16</v>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -665,14 +664,14 @@
       <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>16</v>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -777,7 +776,7 @@
       <c r="C9" s="5">
         <v>10</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>10</v>
       </c>
       <c r="E9" s="5">
@@ -800,7 +799,7 @@
       <c r="C10" s="5">
         <v>10</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>10</v>
       </c>
       <c r="E10" s="5">
@@ -823,7 +822,7 @@
       <c r="C11" s="5">
         <v>10</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>10</v>
       </c>
       <c r="E11" s="5">
@@ -846,7 +845,7 @@
       <c r="C12" s="5">
         <v>10</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>10</v>
       </c>
       <c r="E12" s="5">
@@ -878,13 +877,13 @@
       <c r="F13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>16</v>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FD0CBF-E679-9E48-8BEA-CF88649F5CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504E6BA5-203E-9F40-9B85-62983EDD0E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -139,7 +139,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -168,6 +168,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFA9D08E"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -222,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -232,6 +238,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -693,9 +700,15 @@
       <c r="F5" s="5">
         <v>10</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5" s="5">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -716,9 +729,15 @@
       <c r="F6" s="5">
         <v>10</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="G6" s="9">
+        <v>10</v>
+      </c>
+      <c r="H6" s="9">
+        <v>10</v>
+      </c>
+      <c r="I6" s="9">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504E6BA5-203E-9F40-9B85-62983EDD0E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CDC827-6132-3B43-A619-FFBA15160D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -729,13 +729,13 @@
       <c r="F6" s="5">
         <v>10</v>
       </c>
-      <c r="G6" s="9">
-        <v>10</v>
-      </c>
-      <c r="H6" s="9">
-        <v>10</v>
-      </c>
-      <c r="I6" s="9">
+      <c r="G6" s="5">
+        <v>10</v>
+      </c>
+      <c r="H6" s="5">
+        <v>10</v>
+      </c>
+      <c r="I6" s="5">
         <v>10</v>
       </c>
     </row>
@@ -758,9 +758,15 @@
       <c r="F7" s="5">
         <v>10</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="G7" s="9">
+        <v>10</v>
+      </c>
+      <c r="H7" s="9">
+        <v>10</v>
+      </c>
+      <c r="I7" s="9">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CDC827-6132-3B43-A619-FFBA15160D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE576A16-1584-B841-A93F-C73634140B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -173,11 +173,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -224,11 +224,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -238,7 +247,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,13 +768,13 @@
       <c r="F7" s="5">
         <v>10</v>
       </c>
-      <c r="G7" s="9">
-        <v>10</v>
-      </c>
-      <c r="H7" s="9">
-        <v>10</v>
-      </c>
-      <c r="I7" s="9">
+      <c r="G7" s="5">
+        <v>10</v>
+      </c>
+      <c r="H7" s="5">
+        <v>10</v>
+      </c>
+      <c r="I7" s="5">
         <v>10</v>
       </c>
     </row>
@@ -787,9 +797,15 @@
       <c r="F8" s="5">
         <v>10</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="G8" s="5">
+        <v>10</v>
+      </c>
+      <c r="H8" s="5">
+        <v>10</v>
+      </c>
+      <c r="I8" s="5">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -810,9 +826,15 @@
       <c r="F9" s="5">
         <v>10</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="G9" s="5">
+        <v>10</v>
+      </c>
+      <c r="H9" s="5">
+        <v>10</v>
+      </c>
+      <c r="I9" s="5">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -833,9 +855,15 @@
       <c r="F10" s="5">
         <v>10</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="G10" s="5">
+        <v>10</v>
+      </c>
+      <c r="H10" s="5">
+        <v>10</v>
+      </c>
+      <c r="I10" s="5">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -856,9 +884,15 @@
       <c r="F11" s="5">
         <v>10</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="G11" s="9">
+        <v>10</v>
+      </c>
+      <c r="H11" s="10">
+        <v>10</v>
+      </c>
+      <c r="I11" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishamody/Desktop/lbllm_behavioral/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE576A16-1584-B841-A93F-C73634140B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75D6656-2405-1B47-98E5-5E8AFDFC20CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="680" windowWidth="21240" windowHeight="16020" xr2:uid="{5B3AD313-C567-A344-8F15-1E4D671AA27F}"/>
   </bookViews>
@@ -884,13 +884,13 @@
       <c r="F11" s="5">
         <v>10</v>
       </c>
-      <c r="G11" s="9">
-        <v>10</v>
-      </c>
-      <c r="H11" s="10">
-        <v>10</v>
-      </c>
-      <c r="I11" s="10">
+      <c r="G11" s="5">
+        <v>10</v>
+      </c>
+      <c r="H11" s="5">
+        <v>10</v>
+      </c>
+      <c r="I11" s="5">
         <v>10</v>
       </c>
     </row>
@@ -913,9 +913,15 @@
       <c r="F12" s="5">
         <v>10</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="G12" s="9">
+        <v>10</v>
+      </c>
+      <c r="H12" s="10">
+        <v>10</v>
+      </c>
+      <c r="I12" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
